--- a/artfynd/A 36893-2025 artfynd.xlsx
+++ b/artfynd/A 36893-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107698240</v>
+        <v>107698234</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V Storrukstjärnren, Täftelandet, Vb</t>
+          <t>N Märratjärnen, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>771988.5903523911</v>
+        <v>772396</v>
       </c>
       <c r="R2" t="n">
-        <v>7087717.86748586</v>
+        <v>7087770</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>granstubbe</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,50 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107698234</v>
+        <v>107698191</v>
       </c>
       <c r="B3" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Märratjärnen, Täftelandet, Vb</t>
+          <t>V Storrukstjärnren, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772396.0270129489</v>
+        <v>772060</v>
       </c>
       <c r="R3" t="n">
-        <v>7087770.149312913</v>
+        <v>7087773</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,21 +845,11 @@
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,11 +858,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>granstubbe</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -904,19 +874,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107698237</v>
+        <v>107698230</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -940,14 +905,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>V Storrukstjärnren, Täftelandet, Vb</t>
+          <t>O Märratjärnen, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772233.4633584686</v>
+        <v>772610</v>
       </c>
       <c r="R4" t="n">
-        <v>7087804.834378574</v>
+        <v>7087726</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,19 +942,9 @@
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-03-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,55 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107698238</v>
+        <v>107698231</v>
       </c>
       <c r="B5" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>V Storrukstjärnren, Täftelandet, Vb</t>
+          <t>O Märratjärnen, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772225.6955147139</v>
+        <v>772567</v>
       </c>
       <c r="R5" t="n">
-        <v>7087797.057708203</v>
+        <v>7087720</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1039,9 @@
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,59 +1068,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107698239</v>
+        <v>107698237</v>
       </c>
       <c r="B6" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>V Storrukstjärnren, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>771992.848245586</v>
+        <v>772233</v>
       </c>
       <c r="R6" t="n">
-        <v>7087720.012677619</v>
+        <v>7087805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,19 +1136,9 @@
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-03-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,19 +1165,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107698230</v>
+        <v>107698240</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1290,14 +1196,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>O Märratjärnen, Täftelandet, Vb</t>
+          <t>V Storrukstjärnren, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>772609.6658453229</v>
+        <v>771989</v>
       </c>
       <c r="R7" t="n">
-        <v>7087725.714128166</v>
+        <v>7087718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,19 +1233,9 @@
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-03-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,50 +1262,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107698233</v>
+        <v>107698238</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Märratjärnen, Täftelandet, Vb</t>
+          <t>V Storrukstjärnren, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>772400.93686776</v>
+        <v>772226</v>
       </c>
       <c r="R8" t="n">
-        <v>7087775.014854632</v>
+        <v>7087797</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,21 +1335,11 @@
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1462,11 +1348,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>granstubbe</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1483,50 +1364,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107698191</v>
+        <v>107698232</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>V Storrukstjärnren, Täftelandet, Vb</t>
+          <t>N Märratjärnen, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>772059.8074577879</v>
+        <v>772458</v>
       </c>
       <c r="R9" t="n">
-        <v>7087772.876155714</v>
+        <v>7087782</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,19 +1441,9 @@
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-03-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,19 +1470,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107698232</v>
+        <v>107698239</v>
       </c>
       <c r="B10" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1640,14 +1510,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N Märratjärnen, Täftelandet, Vb</t>
+          <t>V Storrukstjärnren, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>772457.6838242335</v>
+        <v>771993</v>
       </c>
       <c r="R10" t="n">
-        <v>7087781.727232599</v>
+        <v>7087720</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,19 +1547,9 @@
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-03-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 36893-2025 artfynd.xlsx
+++ b/artfynd/A 36893-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698234</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698191</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698230</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698231</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698237</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698240</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698238</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698232</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,8 +1618,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698239</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>